--- a/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,108 +486,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0006</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>60SK HYNIX INC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.18%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>11410</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>2000</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0091</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.68%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.97%</t>
-        </is>
-      </c>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>30192</v>
-      </c>
-      <c r="K3" t="n">
-        <v>18688</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-11,504</t>
-        </is>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -599,37 +581,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1025000</v>
+      </c>
       <c r="K4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>595000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-430,000</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>2026-09-01_00407A_full_holdings.xlsx</t>
@@ -644,164 +644,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.69%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>191191</v>
+      </c>
+      <c r="K5" t="n">
+        <v>67000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-124,191</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2.12%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.16%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.96%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1025000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>595000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-430,000</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.69%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>191191</v>
-      </c>
-      <c r="K7" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-124,191</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>2026-09-01_00407A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,90 +486,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="J2" t="n">
+        <v>11410</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>0091</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>30192</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18688</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-11,504</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -581,55 +599,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2.12%</t>
-        </is>
-      </c>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.16%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.96%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1025000</v>
-      </c>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>595000</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-430,000</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>2026-09-01_00407A_full_holdings.xlsx</t>
@@ -644,56 +644,164 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>595000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-430,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>藥華藥</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>藥華藥</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>1.02%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.33%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>-0.69%</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J7" t="n">
         <v>191191</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K7" t="n">
         <v>67000</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>-124,191</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-09-01_00407A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,52 +486,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0006</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.18%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.65%</t>
+        </is>
+      </c>
       <c r="J2" t="n">
-        <v>11410</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>2612000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1577000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-1,035,000</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -541,150 +559,186 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0091</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30192</v>
+        <v>171000</v>
       </c>
       <c r="K3" t="n">
-        <v>18688</v>
+        <v>804000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-11,504</t>
+          <t>633,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>致茂電子</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>致茂電子</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5000</v>
+      </c>
       <c r="K4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>43000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>38,000</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>2.48%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>47000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -694,116 +748,4391 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1025000</v>
+        <v>146000</v>
       </c>
       <c r="K6" t="n">
-        <v>595000</v>
+        <v>313000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-430,000</t>
+          <t>167,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>475000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-448,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>202000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>252000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>95000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>105000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>環球晶圓</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>環球晶圓</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+1.54%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>174000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>164,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.61%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>56000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-13,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>11410</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0091</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>30192</v>
+      </c>
+      <c r="K15" t="n">
+        <v>18688</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-11,504</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>00407A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>595000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-430,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>藥華藥</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>藥華藥</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>1.02%</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.33%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>-0.69%</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J19" t="n">
         <v>191191</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K19" t="n">
         <v>67000</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-124,191</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>821000</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>78000</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>59000</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>149000</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>健鼎科技</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>43000</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>177000</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>171000</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>173000</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>77000</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>45000</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>57000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>175000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-88,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1435000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-97,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>243000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>202000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-41,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8.39%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>378000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>363000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>444000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>106,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-114,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>151000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>140000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>567000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>524000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-43,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>41000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>72,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>114000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>106000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>59000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>778000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>763000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>41000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-41,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1458000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>729000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-729,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>773360</v>
+      </c>
+      <c r="K52" t="n">
+        <v>439360</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-334,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1134220</v>
+      </c>
+      <c r="K53" t="n">
+        <v>566220</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-568,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>158000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-24,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4.19%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>563000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>454000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-109,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>354000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>304000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>260000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>611000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>351,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>195000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>367000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>172,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>48000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>88000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>25600</v>
+      </c>
+      <c r="K66" t="n">
+        <v>20600</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>94872</v>
+      </c>
+      <c r="K67" t="n">
+        <v>73872</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-21,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>48000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>54,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>38000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>79000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-40,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-33,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>306000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-57,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>39000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-33,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>55000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>47000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-13,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>247000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>216000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>87000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>108000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>48,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>9.21%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>9.17%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2612000</v>
+        <v>4757000</v>
       </c>
       <c r="K2" t="n">
-        <v>1577000</v>
+        <v>4750000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-1,035,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,60 +559,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>171000</v>
+        <v>5916000</v>
       </c>
       <c r="K3" t="n">
-        <v>804000</v>
+        <v>5028000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>633,000</t>
+          <t>-888,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,60 +622,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5000</v>
+        <v>18679000</v>
       </c>
       <c r="K4" t="n">
-        <v>43000</v>
+        <v>16811000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>38,000</t>
+          <t>-1,868,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,60 +685,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>47000</v>
+        <v>8000</v>
       </c>
       <c r="K5" t="n">
-        <v>52000</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -753,55 +753,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>146000</v>
+        <v>477000</v>
       </c>
       <c r="K6" t="n">
-        <v>313000</v>
+        <v>561000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>84,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -811,60 +811,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>5.83%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>475000</v>
+        <v>2176000</v>
       </c>
       <c r="K7" t="n">
-        <v>27000</v>
+        <v>6490561</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-448,000</t>
+          <t>4,314,561</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -874,60 +874,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>202000</v>
+        <v>1600000</v>
       </c>
       <c r="K8" t="n">
-        <v>252000</v>
+        <v>1450000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>-150,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>95000</v>
+        <v>120500</v>
       </c>
       <c r="K9" t="n">
-        <v>105000</v>
+        <v>140500</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1000,60 +1000,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10000</v>
+        <v>2000000</v>
       </c>
       <c r="K10" t="n">
-        <v>174000</v>
+        <v>1800000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,50 +1073,50 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
+          <t>緯穎科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
+          <t>緯穎科技</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>53000</v>
+        <v>580000</v>
       </c>
       <c r="K11" t="n">
-        <v>56000</v>
+        <v>1730020</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,150,020</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1146,40 +1146,40 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31000</v>
+        <v>300000</v>
       </c>
       <c r="K12" t="n">
-        <v>18000</v>
+        <v>280000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-13,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1209,85 +1209,103 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20000</v>
+        <v>880000</v>
       </c>
       <c r="K13" t="n">
-        <v>9000</v>
+        <v>780000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-01_00985A_full_holdings.xlsx</t>
+          <t>2026-09-01_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0006</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.18%</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>11410</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+        <v>184000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>183000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1302,145 +1320,181 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0091</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30192</v>
+        <v>3273000</v>
       </c>
       <c r="K15" t="n">
-        <v>18688</v>
+        <v>3258000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-11,504</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-01_00990A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5243000</v>
+      </c>
       <c r="K16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>5205000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-38,000</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
       <c r="J17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <v>627000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>621000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1455,55 +1509,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1025000</v>
+        <v>837000</v>
       </c>
       <c r="K18" t="n">
-        <v>595000</v>
+        <v>830000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-430,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1518,730 +1572,1000 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>191191</v>
+        <v>1786000</v>
       </c>
       <c r="K19" t="n">
-        <v>67000</v>
+        <v>1773000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-124,191</t>
+          <t>-13,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4353000</v>
+      </c>
       <c r="K20" t="n">
-        <v>821000</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>4322000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>317000</v>
+      </c>
       <c r="K21" t="n">
-        <v>78000</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>315000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1473000</v>
+      </c>
       <c r="K22" t="n">
-        <v>59000</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>1466000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>興勤</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>興勤</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2337000</v>
+      </c>
       <c r="K23" t="n">
-        <v>13000</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>2318000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6.04%</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>6.08%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>742000</v>
+      </c>
       <c r="K24" t="n">
-        <v>149000</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>736000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1562000</v>
+      </c>
       <c r="K25" t="n">
-        <v>97000</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>1553000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1294000</v>
+      </c>
       <c r="K26" t="n">
-        <v>43000</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
+        <v>1285000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>大毅</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>大毅</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>4451000</v>
+      </c>
       <c r="K27" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>4418000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-33,000</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>3.83%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>255000</v>
+      </c>
       <c r="K28" t="n">
-        <v>177000</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>254000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>2.39%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>376000</v>
+      </c>
       <c r="K29" t="n">
-        <v>171000</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>374000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>日電貿</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>日電貿</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3371000</v>
+      </c>
       <c r="K30" t="n">
-        <v>173000</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>3346000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-25,000</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3405000</v>
+      </c>
       <c r="K31" t="n">
-        <v>77000</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>3404000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3445000</v>
+      </c>
       <c r="K32" t="n">
-        <v>45000</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>3418000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-27,000</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>碩天</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>碩天</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>591000</v>
+      </c>
       <c r="K33" t="n">
-        <v>36000</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>579000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-12,000</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>950000</v>
+      </c>
       <c r="K34" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>942000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2256,55 +2580,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>57000</v>
+        <v>3178000</v>
       </c>
       <c r="K35" t="n">
-        <v>28000</v>
+        <v>3158000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-29,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2319,55 +2643,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>32000</v>
+        <v>6468000</v>
       </c>
       <c r="K36" t="n">
-        <v>30000</v>
+        <v>6445000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-23,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2382,55 +2706,55 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>175000</v>
+        <v>3506000</v>
       </c>
       <c r="K37" t="n">
-        <v>87000</v>
+        <v>3481000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-25,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2445,55 +2769,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1435000</v>
+        <v>459000</v>
       </c>
       <c r="K38" t="n">
-        <v>1338000</v>
+        <v>455000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-97,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2508,55 +2832,55 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>243000</v>
+        <v>3800000</v>
       </c>
       <c r="K39" t="n">
-        <v>202000</v>
+        <v>3771000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-41,000</t>
+          <t>-29,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2571,55 +2895,55 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8.39%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>378000</v>
+        <v>307000</v>
       </c>
       <c r="K40" t="n">
-        <v>363000</v>
+        <v>305000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2629,60 +2953,60 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>444000</v>
+        <v>431000</v>
       </c>
       <c r="K41" t="n">
-        <v>550000</v>
+        <v>428000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>106,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2697,55 +3021,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1610000</v>
+        <v>1108000</v>
       </c>
       <c r="K42" t="n">
-        <v>1496000</v>
+        <v>1100000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-114,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2755,60 +3079,60 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>7.51%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>151000</v>
+        <v>510000</v>
       </c>
       <c r="K43" t="n">
-        <v>140000</v>
+        <v>1391225</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>881,225</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2823,55 +3147,55 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>567000</v>
+        <v>541000</v>
       </c>
       <c r="K44" t="n">
-        <v>524000</v>
+        <v>537000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-43,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2886,244 +3210,190 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>22000</v>
+        <v>2839000</v>
       </c>
       <c r="K45" t="n">
-        <v>11000</v>
+        <v>2807000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-32,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>+0.86%</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>41000</v>
-      </c>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
-        <v>113000</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>72,000</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>台光電子</t>
-        </is>
-      </c>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>台光電子</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>6.07%</t>
-        </is>
-      </c>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5.68%</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-0.39%</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>114000</v>
-      </c>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>106000</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
+        <v>1200000</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>59000</v>
-      </c>
-      <c r="K48" t="n">
-        <v>29000</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-30,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3133,60 +3403,60 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>778000</v>
+        <v>12000000</v>
       </c>
       <c r="K49" t="n">
-        <v>763000</v>
+        <v>13500000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3201,55 +3471,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>82000</v>
+        <v>2880000</v>
       </c>
       <c r="K50" t="n">
-        <v>41000</v>
+        <v>2750000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-41,000</t>
+          <t>-130,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3264,55 +3534,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>15.86%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1458000</v>
+        <v>10800000</v>
       </c>
       <c r="K51" t="n">
-        <v>729000</v>
+        <v>10500000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-729,000</t>
+          <t>-300,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3327,55 +3597,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>773360</v>
+        <v>3000000</v>
       </c>
       <c r="K52" t="n">
-        <v>439360</v>
+        <v>2000000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-334,000</t>
+          <t>-1,000,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3390,55 +3660,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1134220</v>
+        <v>7000000</v>
       </c>
       <c r="K53" t="n">
-        <v>566220</v>
+        <v>5000000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-568,000</t>
+          <t>-2,000,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3448,60 +3718,60 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>158000</v>
+        <v>860000</v>
       </c>
       <c r="K54" t="n">
-        <v>134000</v>
+        <v>1100000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3516,55 +3786,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>563000</v>
+        <v>6000000</v>
       </c>
       <c r="K55" t="n">
-        <v>454000</v>
+        <v>4500000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-109,000</t>
+          <t>-1,500,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3579,55 +3849,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>25000</v>
+        <v>149500</v>
       </c>
       <c r="K56" t="n">
-        <v>37000</v>
+        <v>189500</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3637,60 +3907,60 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>354000</v>
+        <v>700000</v>
       </c>
       <c r="K57" t="n">
-        <v>304000</v>
+        <v>2087956</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>1,387,956</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3700,60 +3970,60 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>260000</v>
+        <v>1050000</v>
       </c>
       <c r="K58" t="n">
-        <v>611000</v>
+        <v>850000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>351,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3763,60 +4033,60 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>195000</v>
+        <v>600000</v>
       </c>
       <c r="K59" t="n">
-        <v>367000</v>
+        <v>400000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>172,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3826,60 +4096,60 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>48000</v>
+        <v>2612000</v>
       </c>
       <c r="K60" t="n">
-        <v>50000</v>
+        <v>1577000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-1,035,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3889,60 +4159,60 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>32000</v>
+        <v>171000</v>
       </c>
       <c r="K61" t="n">
-        <v>16000</v>
+        <v>804000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-16,000</t>
+          <t>633,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3952,60 +4222,60 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>致茂電子</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>致茂電子</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>36000</v>
+        <v>5000</v>
       </c>
       <c r="K62" t="n">
-        <v>29000</v>
+        <v>43000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>38,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4015,60 +4285,60 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>8000</v>
+        <v>47000</v>
       </c>
       <c r="K63" t="n">
-        <v>4000</v>
+        <v>52000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4083,55 +4353,55 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>88000</v>
+        <v>146000</v>
       </c>
       <c r="K64" t="n">
-        <v>90000</v>
+        <v>313000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>167,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4146,55 +4416,55 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>200000</v>
+        <v>475000</v>
       </c>
       <c r="K65" t="n">
-        <v>100000</v>
+        <v>27000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-448,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4204,60 +4474,60 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>25600</v>
+        <v>202000</v>
       </c>
       <c r="K66" t="n">
-        <v>20600</v>
+        <v>252000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4267,60 +4537,60 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>94872</v>
+        <v>95000</v>
       </c>
       <c r="K67" t="n">
-        <v>73872</v>
+        <v>105000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4335,55 +4605,55 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>48000</v>
+        <v>10000</v>
       </c>
       <c r="K68" t="n">
-        <v>102000</v>
+        <v>174000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>54,000</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4393,60 +4663,60 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>38000</v>
+        <v>53000</v>
       </c>
       <c r="K69" t="n">
-        <v>19000</v>
+        <v>56000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-19,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4461,55 +4731,55 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>79000</v>
+        <v>31000</v>
       </c>
       <c r="K70" t="n">
-        <v>39000</v>
+        <v>18000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-40,000</t>
+          <t>-13,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4524,55 +4794,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>66000</v>
+        <v>20000</v>
       </c>
       <c r="K71" t="n">
-        <v>33000</v>
+        <v>9000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-33,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4587,55 +4857,55 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>306000</v>
+        <v>343000</v>
       </c>
       <c r="K72" t="n">
-        <v>249000</v>
+        <v>293000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-57,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4645,123 +4915,105 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>39000</v>
+        <v>77000</v>
       </c>
       <c r="K73" t="n">
-        <v>34000</v>
+        <v>229675</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>152,675</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>0006</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K74" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>-33,000</t>
-        </is>
-      </c>
+        <v>11410</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4776,55 +5028,55 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>0091</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>55000</v>
+        <v>30192</v>
       </c>
       <c r="K75" t="n">
-        <v>47000</v>
+        <v>18688</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-11,504</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4839,55 +5091,55 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>7.71%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>26000</v>
+        <v>658000</v>
       </c>
       <c r="K76" t="n">
-        <v>13000</v>
+        <v>558000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-13,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4902,55 +5154,55 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>7.48%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>6.37%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>247000</v>
+        <v>370000</v>
       </c>
       <c r="K77" t="n">
-        <v>216000</v>
+        <v>310000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>-60,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4960,179 +5212,3905 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>36000</v>
+        <v>50000</v>
       </c>
       <c r="K78" t="n">
-        <v>31000</v>
+        <v>149139</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>99,139</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>87000</v>
-      </c>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>21,000</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="K81" t="n">
+        <v>595000</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-430,000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-0.69%</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>191191</v>
+      </c>
+      <c r="K82" t="n">
+        <v>67000</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>-124,191</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-01_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>00993A</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>821000</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="n">
+        <v>78000</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>59000</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>149000</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>健鼎科技</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>43000</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>177000</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>171000</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>173000</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>77000</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>45000</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>57000</v>
+      </c>
+      <c r="K98" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K99" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>175000</v>
+      </c>
+      <c r="K100" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-88,000</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>1435000</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-97,000</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>243000</v>
+      </c>
+      <c r="K102" t="n">
+        <v>202000</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-41,000</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>8.39%</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>378000</v>
+      </c>
+      <c r="K103" t="n">
+        <v>363000</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>444000</v>
+      </c>
+      <c r="K104" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>106,000</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-114,000</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>151000</v>
+      </c>
+      <c r="K106" t="n">
+        <v>140000</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>567000</v>
+      </c>
+      <c r="K107" t="n">
+        <v>524000</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-43,000</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K108" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>41000</v>
+      </c>
+      <c r="K109" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>72,000</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>114000</v>
+      </c>
+      <c r="K110" t="n">
+        <v>106000</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>59000</v>
+      </c>
+      <c r="K111" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>778000</v>
+      </c>
+      <c r="K112" t="n">
+        <v>763000</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K113" t="n">
+        <v>41000</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-41,000</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>1458000</v>
+      </c>
+      <c r="K114" t="n">
+        <v>729000</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>-729,000</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>773360</v>
+      </c>
+      <c r="K115" t="n">
+        <v>439360</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-334,000</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>1134220</v>
+      </c>
+      <c r="K116" t="n">
+        <v>566220</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-568,000</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>158000</v>
+      </c>
+      <c r="K117" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-24,000</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>4.19%</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>563000</v>
+      </c>
+      <c r="K118" t="n">
+        <v>454000</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-109,000</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K119" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>354000</v>
+      </c>
+      <c r="K120" t="n">
+        <v>304000</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>260000</v>
+      </c>
+      <c r="K121" t="n">
+        <v>611000</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>351,000</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>195000</v>
+      </c>
+      <c r="K122" t="n">
+        <v>367000</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>172,000</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>48000</v>
+      </c>
+      <c r="K123" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K124" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K125" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>88000</v>
+      </c>
+      <c r="K127" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K128" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>25600</v>
+      </c>
+      <c r="K129" t="n">
+        <v>20600</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>94872</v>
+      </c>
+      <c r="K130" t="n">
+        <v>73872</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>-21,000</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>48000</v>
+      </c>
+      <c r="K131" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>54,000</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>38000</v>
+      </c>
+      <c r="K132" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>79000</v>
+      </c>
+      <c r="K133" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-40,000</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K134" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>-33,000</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>306000</v>
+      </c>
+      <c r="K135" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>-57,000</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>39000</v>
+      </c>
+      <c r="K136" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K137" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-33,000</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>55000</v>
+      </c>
+      <c r="K138" t="n">
+        <v>47000</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K139" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-13,000</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>247000</v>
+      </c>
+      <c r="K140" t="n">
+        <v>216000</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K141" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>87000</v>
+      </c>
+      <c r="K142" t="n">
+        <v>108000</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>0.39%</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>+0.53%</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J143" t="n">
         <v>34000</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K143" t="n">
         <v>82000</v>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t>48,000</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>2026-09-01_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>5.86%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>5.97%</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>221000</v>
+      </c>
+      <c r="K144" t="n">
+        <v>659197</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>438,197</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09-01_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-02_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M144"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5481,3634 +5481,61 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>5.86%</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>5.97%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>221000</v>
+      </c>
       <c r="K83" t="n">
-        <v>821000</v>
-      </c>
-      <c r="L83" t="inlineStr"/>
+        <v>659197</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>438,197</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="n">
-        <v>78000</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="n">
-        <v>59000</v>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="n">
-        <v>13000</v>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="n">
-        <v>149000</v>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="n">
-        <v>97000</v>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>健鼎科技</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="n">
-        <v>43000</v>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>弘塑科技</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="n">
-        <v>177000</v>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="n">
-        <v>171000</v>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="n">
-        <v>173000</v>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="n">
-        <v>77000</v>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="n">
-        <v>45000</v>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="n">
-        <v>36000</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>0.38%</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>57000</v>
-      </c>
-      <c r="K98" t="n">
-        <v>28000</v>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>-29,000</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>4.41%</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>4.04%</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-0.37%</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>32000</v>
-      </c>
-      <c r="K99" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>光寶科技</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>光寶科技</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-0.27%</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>175000</v>
-      </c>
-      <c r="K100" t="n">
-        <v>87000</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>-88,000</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>1435000</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>-97,000</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>1.29%</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>1.09%</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>243000</v>
-      </c>
-      <c r="K102" t="n">
-        <v>202000</v>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>-41,000</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>8.84%</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>8.39%</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>378000</v>
-      </c>
-      <c r="K103" t="n">
-        <v>363000</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>-15,000</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>+0.10%</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>444000</v>
-      </c>
-      <c r="K104" t="n">
-        <v>550000</v>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>106,000</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>華邦電子</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>華邦電子</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2.85%</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>1610000</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1496000</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>-114,000</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2.98%</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2.94%</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>151000</v>
-      </c>
-      <c r="K106" t="n">
-        <v>140000</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>-11,000</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>567000</v>
-      </c>
-      <c r="K107" t="n">
-        <v>524000</v>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>-43,000</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K108" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>-11,000</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>+0.86%</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>41000</v>
-      </c>
-      <c r="K109" t="n">
-        <v>113000</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>72,000</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>台光電子</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>台光電子</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>6.07%</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>5.68%</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-0.39%</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>114000</v>
-      </c>
-      <c r="K110" t="n">
-        <v>106000</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>59000</v>
-      </c>
-      <c r="K111" t="n">
-        <v>29000</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>-30,000</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>4.10%</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>3.76%</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-0.34%</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>778000</v>
-      </c>
-      <c r="K112" t="n">
-        <v>763000</v>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>-15,000</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-0.25%</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>82000</v>
-      </c>
-      <c r="K113" t="n">
-        <v>41000</v>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>-41,000</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>凱基金控</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>凱基金控</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>1458000</v>
-      </c>
-      <c r="K114" t="n">
-        <v>729000</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>-729,000</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>773360</v>
-      </c>
-      <c r="K115" t="n">
-        <v>439360</v>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>-334,000</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>永豐金控</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>永豐金控</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>0.22%</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>1134220</v>
-      </c>
-      <c r="K116" t="n">
-        <v>566220</v>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>-568,000</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>4.34%</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-0.92%</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>158000</v>
-      </c>
-      <c r="K117" t="n">
-        <v>134000</v>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>-24,000</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>5.46%</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>4.19%</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-1.27%</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>563000</v>
-      </c>
-      <c r="K118" t="n">
-        <v>454000</v>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>-109,000</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>聯亞光電</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>聯亞光電</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>0.86%</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>1.20%</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>+0.34%</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K119" t="n">
-        <v>37000</v>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2.82%</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>2.53%</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>354000</v>
-      </c>
-      <c r="K120" t="n">
-        <v>304000</v>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>-50,000</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>260000</v>
-      </c>
-      <c r="K121" t="n">
-        <v>611000</v>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>351,000</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>+0.40%</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>195000</v>
-      </c>
-      <c r="K122" t="n">
-        <v>367000</v>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>172,000</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>創意電子</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>創意電子</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2.84%</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>2.85%</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>48000</v>
-      </c>
-      <c r="K123" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>昇達科技</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>昇達科技</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>32000</v>
-      </c>
-      <c r="K124" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>-16,000</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>2.09%</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K125" t="n">
-        <v>29000</v>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>-7,000</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-0.16%</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K126" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>-4,000</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>1.85%</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>+0.13%</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>88000</v>
-      </c>
-      <c r="K127" t="n">
-        <v>90000</v>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>1.13%</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-0.55%</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K128" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>3.99%</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>3.35%</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-0.64%</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
-        <v>25600</v>
-      </c>
-      <c r="K129" t="n">
-        <v>20600</v>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>1.34%</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
-        </is>
-      </c>
-      <c r="J130" t="n">
-        <v>94872</v>
-      </c>
-      <c r="K130" t="n">
-        <v>73872</v>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>-21,000</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>亞翔工程</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>亞翔工程</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>+0.40%</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>48000</v>
-      </c>
-      <c r="K131" t="n">
-        <v>102000</v>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>54,000</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-0.25%</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>38000</v>
-      </c>
-      <c r="K132" t="n">
-        <v>19000</v>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>-19,000</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>6196</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>79000</v>
-      </c>
-      <c r="K133" t="n">
-        <v>39000</v>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>-40,000</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>66000</v>
-      </c>
-      <c r="K134" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>-33,000</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>4.26%</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>3.43%</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-0.83%</t>
-        </is>
-      </c>
-      <c r="J135" t="n">
-        <v>306000</v>
-      </c>
-      <c r="K135" t="n">
-        <v>249000</v>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>-57,000</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>2.38%</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-0.15%</t>
-        </is>
-      </c>
-      <c r="J136" t="n">
-        <v>39000</v>
-      </c>
-      <c r="K136" t="n">
-        <v>34000</v>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>6584</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K137" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>-33,000</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-0.30%</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>55000</v>
-      </c>
-      <c r="K138" t="n">
-        <v>47000</v>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>0.73%</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-0.75%</t>
-        </is>
-      </c>
-      <c r="J139" t="n">
-        <v>26000</v>
-      </c>
-      <c r="K139" t="n">
-        <v>13000</v>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>-13,000</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>2.95%</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2.52%</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-0.43%</t>
-        </is>
-      </c>
-      <c r="J140" t="n">
-        <v>247000</v>
-      </c>
-      <c r="K140" t="n">
-        <v>216000</v>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>-31,000</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="J141" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K141" t="n">
-        <v>31000</v>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="J142" t="n">
-        <v>87000</v>
-      </c>
-      <c r="K142" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>21,000</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>+0.53%</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K143" t="n">
-        <v>82000</v>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>48,000</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>2026-09-01_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>5.86%</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>5.97%</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="J144" t="n">
-        <v>221000</v>
-      </c>
-      <c r="K144" t="n">
-        <v>659197</v>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>438,197</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
         <is>
           <t>2026-09-01_00400A_full_holdings.xlsx</t>
         </is>
